--- a/artfynd/A 418-2026 artfynd.xlsx
+++ b/artfynd/A 418-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113018043</v>
+        <v>112038636</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620645</v>
+        <v>620541</v>
       </c>
       <c r="R3" t="n">
-        <v>6907289</v>
+        <v>6907017</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,13 +883,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113018043</t>
+          <t>https://artportalen.se/Sighting/112038636</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129577446</v>
+        <v>113018043</v>
       </c>
       <c r="B4" t="n">
         <v>91909</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620486</v>
+        <v>620645</v>
       </c>
       <c r="R4" t="n">
-        <v>6907249</v>
+        <v>6907289</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,16 +985,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129577446</t>
+          <t>https://artportalen.se/Sighting/113018043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132627017</v>
+        <v>129576405</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,14 +1022,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620567</v>
+        <v>620599</v>
       </c>
       <c r="R5" t="n">
-        <v>6907210</v>
+        <v>6906925</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,62 +1076,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627017</t>
+          <t>https://artportalen.se/Sighting/129576405</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133816706</v>
+        <v>129577446</v>
       </c>
       <c r="B6" t="n">
-        <v>79912</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620552</v>
+        <v>620486</v>
       </c>
       <c r="R6" t="n">
-        <v>6907124</v>
+        <v>6907249</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,38 +1189,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133816706</t>
+          <t>https://artportalen.se/Sighting/129577446</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132627032</v>
+        <v>132627017</v>
       </c>
       <c r="B7" t="n">
-        <v>96413</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620624</v>
+        <v>620567</v>
       </c>
       <c r="R7" t="n">
-        <v>6907248</v>
+        <v>6907210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1291,51 +1291,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627032</t>
+          <t>https://artportalen.se/Sighting/132627017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127291532</v>
+        <v>133816705</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>79912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620569</v>
+        <v>620550</v>
       </c>
       <c r="R8" t="n">
-        <v>6907190</v>
+        <v>6907041</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,22 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,51 +1397,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127291532</t>
+          <t>https://artportalen.se/Sighting/133816705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112038656</v>
+        <v>133816706</v>
       </c>
       <c r="B9" t="n">
-        <v>91443</v>
+        <v>79912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>1353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620484</v>
+        <v>620552</v>
       </c>
       <c r="R9" t="n">
-        <v>6907328</v>
+        <v>6907124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1474,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,51 +1499,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112038656</t>
+          <t>https://artportalen.se/Sighting/133816706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291446</v>
+        <v>132627032</v>
       </c>
       <c r="B10" t="n">
-        <v>91443</v>
+        <v>96413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5754</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620539</v>
+        <v>620624</v>
       </c>
       <c r="R10" t="n">
-        <v>6907155</v>
+        <v>6907248</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1576,22 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,71 +1590,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127291446</t>
+          <t>https://artportalen.se/Sighting/132627032</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129577482</v>
+        <v>127291532</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620471</v>
+        <v>620569</v>
       </c>
       <c r="R11" t="n">
-        <v>6907238</v>
+        <v>6907190</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1697,12 +1672,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,51 +1713,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129577482</t>
+          <t>https://artportalen.se/Sighting/127291532</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129578097</v>
+        <v>136595649</v>
       </c>
       <c r="B12" t="n">
-        <v>80336</v>
+        <v>93433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620464</v>
+        <v>620557</v>
       </c>
       <c r="R12" t="n">
-        <v>6907252</v>
+        <v>6906981</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1799,12 +1784,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,16 +1815,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129578097</t>
+          <t>https://artportalen.se/Sighting/136595649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127291750</v>
+        <v>112038656</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>91443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,51 +1832,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5754</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620622</v>
+        <v>620484</v>
       </c>
       <c r="R13" t="n">
-        <v>6907237</v>
+        <v>6907328</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,22 +1886,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,16 +1917,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127291750</t>
+          <t>https://artportalen.se/Sighting/112038656</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132627014</v>
+        <v>127291446</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>91443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,42 +1934,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5754</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620542</v>
+        <v>620539</v>
       </c>
       <c r="R14" t="n">
-        <v>6907069</v>
+        <v>6907155</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2032,12 +1988,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,70 +2018,74 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627014</t>
+          <t>https://artportalen.se/Sighting/127291446</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132627015</v>
+        <v>129577482</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620554</v>
+        <v>620471</v>
       </c>
       <c r="R15" t="n">
-        <v>6907215</v>
+        <v>6907238</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,17 +2109,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,69 +2129,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627015</t>
+          <t>https://artportalen.se/Sighting/129577482</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102531543</v>
+        <v>129578097</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620444</v>
+        <v>620464</v>
       </c>
       <c r="R16" t="n">
-        <v>6907301</v>
+        <v>6907252</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,12 +2211,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,7 +2225,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2282,58 +2242,68 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102531543</t>
+          <t>https://artportalen.se/Sighting/129578097</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102531588</v>
+        <v>127291750</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620593</v>
+        <v>620622</v>
       </c>
       <c r="R17" t="n">
-        <v>6907289</v>
+        <v>6907237</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2357,12 +2327,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,7 +2351,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2389,58 +2368,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102531588</t>
+          <t>https://artportalen.se/Sighting/127291750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102531602</v>
+        <v>132627014</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620635</v>
+        <v>620542</v>
       </c>
       <c r="R18" t="n">
-        <v>6907258</v>
+        <v>6907069</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2464,12 +2444,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2478,72 +2458,76 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102531602</t>
+          <t>https://artportalen.se/Sighting/132627014</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132627016</v>
+        <v>132627015</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620553</v>
+        <v>620554</v>
       </c>
       <c r="R19" t="n">
-        <v>6907206</v>
+        <v>6907215</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2577,7 +2561,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,51 +2587,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627016</t>
+          <t>https://artportalen.se/Sighting/132627015</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132627018</v>
+        <v>136595648</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620569</v>
+        <v>620571</v>
       </c>
       <c r="R20" t="n">
-        <v>6907223</v>
+        <v>6906943</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2674,17 +2663,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100 bladrosetter</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,27 +2683,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627018</t>
+          <t>https://artportalen.se/Sighting/136595648</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132627019</v>
+        <v>102531187</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2745,19 +2729,23 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620612</v>
+        <v>620452</v>
       </c>
       <c r="R21" t="n">
-        <v>6907246</v>
+        <v>6907058</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2781,17 +2769,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,33 +2783,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627019</t>
+          <t>https://artportalen.se/Sighting/102531187</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132627020</v>
+        <v>102531543</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,19 +2836,23 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620612</v>
+        <v>620444</v>
       </c>
       <c r="R22" t="n">
-        <v>6907283</v>
+        <v>6907301</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2888,17 +2876,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,33 +2890,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627020</t>
+          <t>https://artportalen.se/Sighting/102531543</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132627021</v>
+        <v>102531588</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,19 +2943,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620605</v>
+        <v>620593</v>
       </c>
       <c r="R23" t="n">
-        <v>6907280</v>
+        <v>6907289</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2995,17 +2983,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,33 +2997,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627021</t>
+          <t>https://artportalen.se/Sighting/102531588</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132627022</v>
+        <v>102531602</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,19 +3050,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620576</v>
+        <v>620635</v>
       </c>
       <c r="R24" t="n">
-        <v>6907314</v>
+        <v>6907258</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3102,17 +3090,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,33 +3104,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627022</t>
+          <t>https://artportalen.se/Sighting/102531602</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132627023</v>
+        <v>102531620</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,19 +3157,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620566</v>
+        <v>620662</v>
       </c>
       <c r="R25" t="n">
-        <v>6907307</v>
+        <v>6907156</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3209,17 +3197,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,30 +3211,31 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627023</t>
+          <t>https://artportalen.se/Sighting/102531620</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132627024</v>
+        <v>132627016</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3286,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620566</v>
+        <v>620553</v>
       </c>
       <c r="R26" t="n">
-        <v>6907351</v>
+        <v>6907206</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3326,7 +3310,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,13 +3336,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627024</t>
+          <t>https://artportalen.se/Sighting/132627016</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132627028</v>
+        <v>132627018</v>
       </c>
       <c r="B27" t="n">
         <v>99195</v>
@@ -3393,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620564</v>
+        <v>620569</v>
       </c>
       <c r="R27" t="n">
-        <v>6907355</v>
+        <v>6907223</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3433,7 +3417,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,13 +3443,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627028</t>
+          <t>https://artportalen.se/Sighting/132627018</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132627029</v>
+        <v>132627019</v>
       </c>
       <c r="B28" t="n">
         <v>99195</v>
@@ -3500,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620619</v>
+        <v>620612</v>
       </c>
       <c r="R28" t="n">
-        <v>6907297</v>
+        <v>6907246</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3566,13 +3550,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627029</t>
+          <t>https://artportalen.se/Sighting/132627019</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132627030</v>
+        <v>132627020</v>
       </c>
       <c r="B29" t="n">
         <v>99195</v>
@@ -3607,10 +3591,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620634</v>
+        <v>620612</v>
       </c>
       <c r="R29" t="n">
-        <v>6907281</v>
+        <v>6907283</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3647,7 +3631,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ca 80 bladrosetter</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3673,13 +3657,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627030</t>
+          <t>https://artportalen.se/Sighting/132627020</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132627031</v>
+        <v>132627021</v>
       </c>
       <c r="B30" t="n">
         <v>99195</v>
@@ -3714,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620645</v>
+        <v>620605</v>
       </c>
       <c r="R30" t="n">
-        <v>6907255</v>
+        <v>6907280</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3754,7 +3738,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ca 50 bladroestter</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3780,54 +3764,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132627031</t>
+          <t>https://artportalen.se/Sighting/132627021</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113018042</v>
+        <v>132627022</v>
       </c>
       <c r="B31" t="n">
-        <v>92329</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620606</v>
+        <v>620576</v>
       </c>
       <c r="R31" t="n">
-        <v>6907271</v>
+        <v>6907314</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3854,17 +3835,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3873,69 +3854,68 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113018042</t>
+          <t>https://artportalen.se/Sighting/132627022</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127292086</v>
+        <v>132627023</v>
       </c>
       <c r="B32" t="n">
-        <v>92329</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620510</v>
+        <v>620566</v>
       </c>
       <c r="R32" t="n">
-        <v>6907248</v>
+        <v>6907307</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3962,22 +3942,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,16 +3967,774 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627023</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132627024</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>620566</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6907351</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132627028</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>620564</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6907355</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627028</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132627029</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>620619</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6907297</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627029</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132627030</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>620634</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6907281</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ca 80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627030</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132627031</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>620645</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6907255</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ca 50 bladroestter</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627031</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>113018042</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>620606</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6907271</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018042</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127292086</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>620510</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6907248</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127292086</t>
         </is>
@@ -4040,6 +4773,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
